--- a/lab_3/research.xlsx
+++ b/lab_3/research.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Darowiin\Desktop\labs\ParallelProgramming\lab_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA176267-68E5-4D13-915F-6174CF74DE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068ED2A1-D025-42E6-889E-5D41B495E278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D10AC719-3E9B-4D1A-9DB2-34D703C4A05A}"/>
   </bookViews>
@@ -86,10 +86,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -151,6 +150,14 @@
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
               <a:t> (OpenMP</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> и </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>MPI</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="ru-RU" baseline="0"/>
@@ -1825,7 +1832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB3494B3-F1B5-4984-B712-F6014CDEAB73}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
@@ -2072,24 +2079,6 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E27" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
